--- a/attendance_raw.xlsx
+++ b/attendance_raw.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RegieSapico\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BCFB394-BC9E-43E5-BB2B-8F9B3B9FEDE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C85921D2-3952-42AD-94E9-ED4FF5FBF1AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="supervisor" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="343">
   <si>
     <t>Agyeman, Basheera</t>
   </si>
@@ -109,9 +109,6 @@
     <t>Burgess, Kayla</t>
   </si>
   <si>
-    <t>Busque, Kimberly</t>
-  </si>
-  <si>
     <t>Carrero, David</t>
   </si>
   <si>
@@ -193,15 +190,9 @@
     <t>Gillespie, Millicent</t>
   </si>
   <si>
-    <t>Glenn, Brooke</t>
-  </si>
-  <si>
     <t>Hardwell, A-Je-nae</t>
   </si>
   <si>
-    <t>Hawkins, Monica</t>
-  </si>
-  <si>
     <t>Hay, Ashley</t>
   </si>
   <si>
@@ -421,9 +412,6 @@
     <t>Wiehle, Christoph</t>
   </si>
   <si>
-    <t>Woodlee, Brad</t>
-  </si>
-  <si>
     <t>Woods, Patricia</t>
   </si>
   <si>
@@ -493,9 +481,6 @@
     <t>Martinez-Ramos, Jennifer</t>
   </si>
   <si>
-    <t>McGuire, Linnea</t>
-  </si>
-  <si>
     <t>Meyer, Megan</t>
   </si>
   <si>
@@ -820,9 +805,6 @@
     <t>Smith, Nikki</t>
   </si>
   <si>
-    <t>Corella, David</t>
-  </si>
-  <si>
     <t>CSC, 988</t>
   </si>
   <si>
@@ -913,9 +895,6 @@
     <t>Sagon, Chanell</t>
   </si>
   <si>
-    <t>Sardinas, Albert</t>
-  </si>
-  <si>
     <t>Shifflett, Elizabeth</t>
   </si>
   <si>
@@ -1022,6 +1001,72 @@
   </si>
   <si>
     <t>Admin</t>
+  </si>
+  <si>
+    <t>Armendariz, Domenique</t>
+  </si>
+  <si>
+    <t>Bermudez, Carlos</t>
+  </si>
+  <si>
+    <t>Duong, Chi</t>
+  </si>
+  <si>
+    <t>Emanuel, Mariah</t>
+  </si>
+  <si>
+    <t>Embaugh, Mil</t>
+  </si>
+  <si>
+    <t>Galloway, LaRhonda</t>
+  </si>
+  <si>
+    <t>Gonzalez, Andres</t>
+  </si>
+  <si>
+    <t>Jones, Andrew</t>
+  </si>
+  <si>
+    <t>Lilly, KaNysha</t>
+  </si>
+  <si>
+    <t>Means, Amaria</t>
+  </si>
+  <si>
+    <t>Neidhardt, Kai</t>
+  </si>
+  <si>
+    <t>Nur, Faduma</t>
+  </si>
+  <si>
+    <t>Peet, Richard</t>
+  </si>
+  <si>
+    <t>Radow, Mike</t>
+  </si>
+  <si>
+    <t>Renee, Aary</t>
+  </si>
+  <si>
+    <t>Rose, Lisa</t>
+  </si>
+  <si>
+    <t>Scott, Monica</t>
+  </si>
+  <si>
+    <t>Smith, Katelin</t>
+  </si>
+  <si>
+    <t>Tabason, Abigail</t>
+  </si>
+  <si>
+    <t>Talty, Naomi</t>
+  </si>
+  <si>
+    <t>Williams, TreVaunte</t>
+  </si>
+  <si>
+    <t>Zaragoza, Sharon</t>
   </si>
 </sst>
 </file>
@@ -1416,7 +1461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5807181E-856C-4C1B-8B3E-AC1CE6A3DC63}">
-  <dimension ref="A1:B306"/>
+  <dimension ref="A1:B320"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.5" bestFit="1" customWidth="1"/>
@@ -1425,42 +1470,42 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="B2" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B3" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="B4" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="B5" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -1468,7 +1513,7 @@
         <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>224</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -1476,7 +1521,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -1484,15 +1529,15 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B9" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -1500,7 +1545,7 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -1508,23 +1553,23 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="B12" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B13" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
@@ -1532,1228 +1577,1228 @@
         <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B15" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="B16" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>131</v>
+        <v>321</v>
       </c>
       <c r="B17" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B18" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>215</v>
+        <v>128</v>
       </c>
       <c r="B19" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
+        <v>210</v>
+      </c>
+      <c r="B20" t="s">
         <v>223</v>
-      </c>
-      <c r="B20" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="B21" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>6</v>
+        <v>229</v>
       </c>
       <c r="B22" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>133</v>
+        <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>8</v>
+        <v>129</v>
       </c>
       <c r="B25" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>240</v>
+        <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>9</v>
+        <v>235</v>
       </c>
       <c r="B27" t="s">
-        <v>228</v>
+        <v>305</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>170</v>
+        <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>244</v>
+        <v>165</v>
       </c>
       <c r="B30" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>171</v>
+        <v>239</v>
       </c>
       <c r="B31" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>11</v>
+        <v>166</v>
       </c>
       <c r="B32" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>250</v>
+        <v>322</v>
       </c>
       <c r="B35" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>134</v>
+        <v>13</v>
       </c>
       <c r="B36" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>135</v>
+        <v>245</v>
       </c>
       <c r="B37" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>251</v>
+        <v>130</v>
       </c>
       <c r="B38" t="s">
-        <v>241</v>
+        <v>153</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>14</v>
+        <v>131</v>
       </c>
       <c r="B39" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>15</v>
+        <v>246</v>
       </c>
       <c r="B40" t="s">
-        <v>227</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B41" t="s">
-        <v>252</v>
+        <v>225</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>172</v>
+        <v>15</v>
       </c>
       <c r="B42" t="s">
-        <v>249</v>
+        <v>222</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>253</v>
+        <v>16</v>
       </c>
       <c r="B43" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>17</v>
+        <v>167</v>
       </c>
       <c r="B44" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>309</v>
+        <v>248</v>
       </c>
       <c r="B45" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B46" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>19</v>
+        <v>302</v>
       </c>
       <c r="B47" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B48" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B49" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>136</v>
+        <v>20</v>
       </c>
       <c r="B50" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B51" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>23</v>
+        <v>132</v>
       </c>
       <c r="B52" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>198</v>
+        <v>22</v>
       </c>
       <c r="B53" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>235</v>
+        <v>193</v>
       </c>
       <c r="B54" t="s">
-        <v>255</v>
+        <v>153</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>24</v>
+        <v>230</v>
       </c>
       <c r="B55" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>137</v>
+        <v>23</v>
       </c>
       <c r="B56" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>25</v>
+        <v>133</v>
       </c>
       <c r="B57" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B58" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>173</v>
+        <v>25</v>
       </c>
       <c r="B59" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>256</v>
+        <v>168</v>
       </c>
       <c r="B60" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>199</v>
+        <v>251</v>
       </c>
       <c r="B61" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>230</v>
+        <v>194</v>
       </c>
       <c r="B62" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>27</v>
+        <v>225</v>
       </c>
       <c r="B63" t="s">
-        <v>252</v>
+        <v>218</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>174</v>
+        <v>26</v>
       </c>
       <c r="B64" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="B65" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>28</v>
+        <v>170</v>
       </c>
       <c r="B66" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B67" t="s">
-        <v>228</v>
+        <v>252</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B68" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B69" t="s">
-        <v>247</v>
+        <v>220</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>138</v>
+        <v>30</v>
       </c>
       <c r="B70" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>200</v>
+        <v>134</v>
       </c>
       <c r="B71" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="B72" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B73" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B74" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B75" t="s">
-        <v>241</v>
+        <v>305</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="B76" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="B77" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B78" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="B79" t="s">
-        <v>241</v>
+        <v>305</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B80" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B81" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B82" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B83" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B84" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B85" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B86" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B87" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B88" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B89" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B90" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>140</v>
+        <v>323</v>
       </c>
       <c r="B91" t="s">
-        <v>225</v>
+        <v>249</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>40</v>
+        <v>136</v>
       </c>
       <c r="B92" t="s">
-        <v>249</v>
+        <v>220</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>141</v>
+        <v>39</v>
       </c>
       <c r="B93" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>41</v>
+        <v>324</v>
       </c>
       <c r="B94" t="s">
-        <v>239</v>
+        <v>269</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>42</v>
+        <v>325</v>
       </c>
       <c r="B95" t="s">
-        <v>227</v>
+        <v>298</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>43</v>
+        <v>137</v>
       </c>
       <c r="B96" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B97" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>266</v>
+        <v>41</v>
       </c>
       <c r="B98" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B99" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>267</v>
+        <v>43</v>
       </c>
       <c r="B100" t="s">
-        <v>238</v>
+        <v>219</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>142</v>
+        <v>260</v>
       </c>
       <c r="B101" t="s">
-        <v>246</v>
+        <v>218</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B102" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="B103" t="s">
-        <v>269</v>
+        <v>233</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>270</v>
+        <v>138</v>
       </c>
       <c r="B104" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B105" t="s">
-        <v>259</v>
+        <v>217</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>177</v>
+        <v>262</v>
       </c>
       <c r="B106" t="s">
-        <v>239</v>
+        <v>263</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>48</v>
+        <v>264</v>
       </c>
       <c r="B107" t="s">
-        <v>271</v>
+        <v>245</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>272</v>
+        <v>46</v>
       </c>
       <c r="B108" t="s">
-        <v>224</v>
+        <v>254</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>217</v>
+        <v>172</v>
       </c>
       <c r="B109" t="s">
-        <v>271</v>
+        <v>234</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>273</v>
+        <v>47</v>
       </c>
       <c r="B110" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>143</v>
+        <v>266</v>
       </c>
       <c r="B111" t="s">
-        <v>257</v>
+        <v>219</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>49</v>
+        <v>212</v>
       </c>
       <c r="B112" t="s">
-        <v>242</v>
+        <v>265</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>203</v>
+        <v>267</v>
       </c>
       <c r="B113" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>233</v>
+        <v>326</v>
       </c>
       <c r="B114" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B115" t="s">
-        <v>224</v>
+        <v>252</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>274</v>
+        <v>48</v>
       </c>
       <c r="B116" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="B117" t="s">
-        <v>275</v>
+        <v>237</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>50</v>
+        <v>228</v>
       </c>
       <c r="B118" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>51</v>
+        <v>140</v>
       </c>
       <c r="B119" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="B120" t="s">
-        <v>276</v>
+        <v>305</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>204</v>
+        <v>173</v>
       </c>
       <c r="B121" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>228</v>
+        <v>49</v>
       </c>
       <c r="B122" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>179</v>
+        <v>327</v>
       </c>
       <c r="B123" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="B124" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>145</v>
+        <v>199</v>
       </c>
       <c r="B125" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>277</v>
+        <v>223</v>
       </c>
       <c r="B126" t="s">
-        <v>245</v>
+        <v>305</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>252</v>
+        <v>174</v>
       </c>
       <c r="B127" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>146</v>
+        <v>233</v>
       </c>
       <c r="B128" t="s">
-        <v>246</v>
+        <v>305</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>245</v>
+        <v>141</v>
       </c>
       <c r="B129" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>52</v>
+        <v>271</v>
       </c>
       <c r="B130" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>278</v>
+        <v>247</v>
       </c>
       <c r="B131" t="s">
-        <v>254</v>
+        <v>305</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="B132" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>54</v>
+        <v>240</v>
       </c>
       <c r="B133" t="s">
-        <v>228</v>
+        <v>305</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B134" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>147</v>
+        <v>272</v>
       </c>
       <c r="B135" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>148</v>
+        <v>51</v>
       </c>
       <c r="B136" t="s">
-        <v>275</v>
+        <v>223</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B137" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>236</v>
+        <v>143</v>
       </c>
       <c r="B138" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>247</v>
+        <v>144</v>
       </c>
       <c r="B139" t="s">
-        <v>223</v>
+        <v>269</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>279</v>
+        <v>53</v>
       </c>
       <c r="B140" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="B141" t="s">
-        <v>241</v>
+        <v>218</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>57</v>
+        <v>242</v>
       </c>
       <c r="B142" t="s">
-        <v>252</v>
+        <v>218</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>58</v>
+        <v>273</v>
       </c>
       <c r="B143" t="s">
-        <v>254</v>
+        <v>233</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>59</v>
+        <v>220</v>
       </c>
       <c r="B144" t="s">
-        <v>232</v>
+        <v>305</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>180</v>
+        <v>54</v>
       </c>
       <c r="B145" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>181</v>
+        <v>55</v>
       </c>
       <c r="B146" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>216</v>
+        <v>56</v>
       </c>
       <c r="B147" t="s">
-        <v>247</v>
+        <v>227</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="B148" t="s">
-        <v>251</v>
+        <v>225</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>60</v>
+        <v>176</v>
       </c>
       <c r="B149" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>310</v>
+        <v>211</v>
       </c>
       <c r="B150" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>61</v>
+        <v>177</v>
       </c>
       <c r="B151" t="s">
-        <v>251</v>
+        <v>153</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B152" t="s">
-        <v>225</v>
+        <v>258</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>63</v>
+        <v>303</v>
       </c>
       <c r="B153" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B154" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>183</v>
+        <v>59</v>
       </c>
       <c r="B155" t="s">
-        <v>239</v>
+        <v>220</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>280</v>
+        <v>60</v>
       </c>
       <c r="B156" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B157" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>149</v>
+        <v>178</v>
       </c>
       <c r="B158" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>311</v>
+        <v>328</v>
       </c>
       <c r="B159" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>66</v>
+        <v>274</v>
       </c>
       <c r="B160" t="s">
-        <v>251</v>
+        <v>305</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B161" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>281</v>
+        <v>145</v>
       </c>
       <c r="B162" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>68</v>
+        <v>304</v>
       </c>
       <c r="B163" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B164" t="s">
-        <v>227</v>
+        <v>153</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>205</v>
+        <v>64</v>
       </c>
       <c r="B165" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>206</v>
+        <v>275</v>
       </c>
       <c r="B166" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>257</v>
+        <v>65</v>
       </c>
       <c r="B167" t="s">
         <v>223</v>
@@ -2761,439 +2806,439 @@
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B168" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="B169" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="B170" t="s">
-        <v>259</v>
+        <v>227</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>186</v>
+        <v>252</v>
       </c>
       <c r="B171" t="s">
-        <v>247</v>
+        <v>218</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B172" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>312</v>
+        <v>179</v>
       </c>
       <c r="B173" t="s">
-        <v>305</v>
+        <v>226</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="B174" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>207</v>
+        <v>181</v>
       </c>
       <c r="B175" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B176" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>275</v>
+        <v>305</v>
       </c>
       <c r="B177" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>74</v>
+        <v>329</v>
       </c>
       <c r="B178" t="s">
-        <v>246</v>
+        <v>269</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>269</v>
+        <v>69</v>
       </c>
       <c r="B179" t="s">
-        <v>305</v>
+        <v>252</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="B180" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>208</v>
+        <v>70</v>
       </c>
       <c r="B181" t="s">
-        <v>257</v>
+        <v>223</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>209</v>
+        <v>269</v>
       </c>
       <c r="B182" t="s">
-        <v>251</v>
+        <v>305</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>150</v>
+        <v>71</v>
       </c>
       <c r="B183" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>75</v>
+        <v>263</v>
       </c>
       <c r="B184" t="s">
-        <v>275</v>
+        <v>298</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>271</v>
+        <v>182</v>
       </c>
       <c r="B185" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>241</v>
+        <v>203</v>
       </c>
       <c r="B186" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>76</v>
+        <v>204</v>
       </c>
       <c r="B187" t="s">
-        <v>224</v>
+        <v>153</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>77</v>
+        <v>146</v>
       </c>
       <c r="B188" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>188</v>
+        <v>72</v>
       </c>
       <c r="B189" t="s">
-        <v>236</v>
+        <v>269</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>151</v>
+        <v>265</v>
       </c>
       <c r="B190" t="s">
-        <v>245</v>
+        <v>218</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>282</v>
+        <v>73</v>
       </c>
       <c r="B191" t="s">
-        <v>240</v>
+        <v>219</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B192" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>79</v>
+        <v>183</v>
       </c>
       <c r="B193" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>152</v>
+        <v>276</v>
       </c>
       <c r="B194" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B195" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>81</v>
+        <v>330</v>
       </c>
       <c r="B196" t="s">
-        <v>240</v>
+        <v>153</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>153</v>
+        <v>76</v>
       </c>
       <c r="B197" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="B198" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B199" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>154</v>
+        <v>78</v>
       </c>
       <c r="B200" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>254</v>
+        <v>148</v>
       </c>
       <c r="B201" t="s">
-        <v>241</v>
+        <v>153</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>189</v>
+        <v>79</v>
       </c>
       <c r="B202" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>313</v>
+        <v>80</v>
       </c>
       <c r="B203" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>283</v>
+        <v>331</v>
       </c>
       <c r="B204" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>84</v>
+        <v>149</v>
       </c>
       <c r="B205" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>85</v>
+        <v>249</v>
       </c>
       <c r="B206" t="s">
-        <v>225</v>
+        <v>305</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>155</v>
+        <v>184</v>
       </c>
       <c r="B207" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>190</v>
+        <v>306</v>
       </c>
       <c r="B208" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="B209" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B210" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>87</v>
+        <v>332</v>
       </c>
       <c r="B211" t="s">
-        <v>247</v>
+        <v>298</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
-        <v>210</v>
+        <v>82</v>
       </c>
       <c r="B212" t="s">
-        <v>240</v>
+        <v>220</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>88</v>
+        <v>150</v>
       </c>
       <c r="B213" t="s">
-        <v>259</v>
+        <v>232</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
-        <v>89</v>
+        <v>185</v>
       </c>
       <c r="B214" t="s">
-        <v>226</v>
+        <v>252</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>242</v>
+        <v>278</v>
       </c>
       <c r="B215" t="s">
-        <v>241</v>
+        <v>305</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B216" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>226</v>
+        <v>84</v>
       </c>
       <c r="B217" t="s">
-        <v>223</v>
+        <v>242</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
-        <v>156</v>
+        <v>205</v>
       </c>
       <c r="B218" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
-        <v>211</v>
+        <v>85</v>
       </c>
       <c r="B219" t="s">
-        <v>275</v>
+        <v>254</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B220" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
-        <v>285</v>
+        <v>237</v>
       </c>
       <c r="B221" t="s">
-        <v>225</v>
+        <v>305</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
-        <v>286</v>
+        <v>87</v>
       </c>
       <c r="B222" t="s">
         <v>222</v>
@@ -3201,23 +3246,23 @@
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>265</v>
+        <v>218</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
-        <v>92</v>
+        <v>151</v>
       </c>
       <c r="B224" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
-        <v>93</v>
+        <v>333</v>
       </c>
       <c r="B225" t="s">
         <v>237</v>
@@ -3225,650 +3270,762 @@
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="B226" t="s">
-        <v>223</v>
+        <v>269</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
-        <v>157</v>
+        <v>88</v>
       </c>
       <c r="B227" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
-        <v>94</v>
+        <v>279</v>
       </c>
       <c r="B228" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
-        <v>246</v>
+        <v>280</v>
       </c>
       <c r="B229" t="s">
-        <v>241</v>
+        <v>217</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
-        <v>95</v>
+        <v>232</v>
       </c>
       <c r="B230" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
-        <v>158</v>
+        <v>89</v>
       </c>
       <c r="B231" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B232" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="B233" t="s">
-        <v>250</v>
+        <v>218</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
-        <v>97</v>
+        <v>152</v>
       </c>
       <c r="B234" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="B235" t="s">
-        <v>242</v>
+        <v>221</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
-        <v>99</v>
+        <v>241</v>
       </c>
       <c r="B236" t="s">
-        <v>252</v>
+        <v>305</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="B237" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
-        <v>287</v>
+        <v>153</v>
       </c>
       <c r="B238" t="s">
-        <v>230</v>
+        <v>305</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
-        <v>159</v>
+        <v>93</v>
       </c>
       <c r="B239" t="s">
-        <v>275</v>
+        <v>237</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
-        <v>101</v>
+        <v>334</v>
       </c>
       <c r="B240" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
-        <v>160</v>
+        <v>238</v>
       </c>
       <c r="B241" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B242" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
-        <v>288</v>
+        <v>95</v>
       </c>
       <c r="B243" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
-        <v>232</v>
+        <v>96</v>
       </c>
       <c r="B244" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
-        <v>289</v>
+        <v>97</v>
       </c>
       <c r="B245" t="s">
-        <v>252</v>
+        <v>223</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
-        <v>103</v>
+        <v>281</v>
       </c>
       <c r="B246" t="s">
-        <v>246</v>
+        <v>225</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
-        <v>314</v>
+        <v>154</v>
       </c>
       <c r="B247" t="s">
-        <v>246</v>
+        <v>269</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
-        <v>290</v>
+        <v>98</v>
       </c>
       <c r="B248" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
-        <v>104</v>
+        <v>155</v>
       </c>
       <c r="B249" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
-        <v>105</v>
+        <v>335</v>
       </c>
       <c r="B250" t="s">
-        <v>275</v>
+        <v>243</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
-        <v>276</v>
+        <v>99</v>
       </c>
       <c r="B251" t="s">
-        <v>291</v>
+        <v>232</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="B252" t="s">
-        <v>269</v>
+        <v>228</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
-        <v>161</v>
+        <v>227</v>
       </c>
       <c r="B253" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
-        <v>162</v>
+        <v>336</v>
       </c>
       <c r="B254" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
-        <v>229</v>
+        <v>283</v>
       </c>
       <c r="B255" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B256" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="B257" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
-        <v>107</v>
+        <v>284</v>
       </c>
       <c r="B258" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
-        <v>212</v>
+        <v>101</v>
       </c>
       <c r="B259" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
-        <v>213</v>
+        <v>102</v>
       </c>
       <c r="B260" t="s">
-        <v>243</v>
+        <v>269</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="B261" t="s">
-        <v>241</v>
+        <v>263</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
-        <v>259</v>
+        <v>156</v>
       </c>
       <c r="B262" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B263" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
-        <v>108</v>
+        <v>224</v>
       </c>
       <c r="B264" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B265" t="s">
-        <v>251</v>
+        <v>222</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
-        <v>110</v>
+        <v>337</v>
       </c>
       <c r="B266" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
-        <v>164</v>
+        <v>285</v>
       </c>
       <c r="B267" t="s">
-        <v>275</v>
+        <v>247</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
-        <v>218</v>
+        <v>104</v>
       </c>
       <c r="B268" t="s">
-        <v>252</v>
+        <v>226</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
-        <v>165</v>
+        <v>207</v>
       </c>
       <c r="B269" t="s">
-        <v>245</v>
+        <v>219</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
-        <v>293</v>
+        <v>208</v>
       </c>
       <c r="B270" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
-        <v>248</v>
+        <v>338</v>
       </c>
       <c r="B271" t="s">
-        <v>265</v>
+        <v>241</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
-        <v>111</v>
+        <v>219</v>
       </c>
       <c r="B272" t="s">
-        <v>229</v>
+        <v>305</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="B273" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="B274" t="s">
-        <v>251</v>
+        <v>221</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
-        <v>258</v>
+        <v>105</v>
       </c>
       <c r="B275" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="B276" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
-        <v>192</v>
+        <v>107</v>
       </c>
       <c r="B277" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
-        <v>193</v>
+        <v>159</v>
       </c>
       <c r="B278" t="s">
-        <v>247</v>
+        <v>269</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="B279" t="s">
-        <v>227</v>
+        <v>247</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
-        <v>113</v>
+        <v>160</v>
       </c>
       <c r="B280" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
-        <v>114</v>
+        <v>286</v>
       </c>
       <c r="B281" t="s">
-        <v>237</v>
+        <v>305</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
-        <v>115</v>
+        <v>243</v>
       </c>
       <c r="B282" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B283" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
       <c r="B284" t="s">
-        <v>252</v>
+        <v>233</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B285" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
-        <v>118</v>
+        <v>253</v>
       </c>
       <c r="B286" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
-        <v>214</v>
+        <v>109</v>
       </c>
       <c r="B287" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
-        <v>119</v>
+        <v>187</v>
       </c>
       <c r="B288" t="s">
-        <v>252</v>
+        <v>233</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
-        <v>231</v>
+        <v>339</v>
       </c>
       <c r="B289" t="s">
-        <v>223</v>
+        <v>269</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
-        <v>120</v>
+        <v>340</v>
       </c>
       <c r="B290" t="s">
-        <v>259</v>
+        <v>298</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
-        <v>121</v>
+        <v>188</v>
       </c>
       <c r="B291" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
-        <v>122</v>
+        <v>189</v>
       </c>
       <c r="B292" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="B293" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
-        <v>294</v>
+        <v>111</v>
       </c>
       <c r="B294" t="s">
-        <v>254</v>
+        <v>232</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="B295" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
-        <v>168</v>
+        <v>113</v>
       </c>
       <c r="B296" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="B297" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
-        <v>295</v>
+        <v>162</v>
       </c>
       <c r="B298" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="B299" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="B300" t="s">
-        <v>243</v>
+        <v>219</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="B301" t="s">
-        <v>271</v>
+        <v>247</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
-        <v>128</v>
+        <v>226</v>
       </c>
       <c r="B302" t="s">
-        <v>245</v>
+        <v>218</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
-        <v>296</v>
+        <v>117</v>
       </c>
       <c r="B303" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="B304" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
-        <v>196</v>
+        <v>119</v>
       </c>
       <c r="B305" t="s">
-        <v>259</v>
+        <v>240</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
-        <v>239</v>
+        <v>120</v>
       </c>
       <c r="B306" t="s">
-        <v>223</v>
+        <v>227</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A307" t="s">
+        <v>287</v>
+      </c>
+      <c r="B307" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A308" t="s">
+        <v>121</v>
+      </c>
+      <c r="B308" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A309" t="s">
+        <v>163</v>
+      </c>
+      <c r="B309" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A310" t="s">
+        <v>122</v>
+      </c>
+      <c r="B310" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A311" t="s">
+        <v>288</v>
+      </c>
+      <c r="B311" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A312" t="s">
+        <v>123</v>
+      </c>
+      <c r="B312" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A313" t="s">
+        <v>341</v>
+      </c>
+      <c r="B313" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A314" t="s">
+        <v>190</v>
+      </c>
+      <c r="B314" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A315" t="s">
+        <v>124</v>
+      </c>
+      <c r="B315" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A316" t="s">
+        <v>289</v>
+      </c>
+      <c r="B316" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A317" t="s">
+        <v>125</v>
+      </c>
+      <c r="B317" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A318" t="s">
+        <v>191</v>
+      </c>
+      <c r="B318" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A319" t="s">
+        <v>342</v>
+      </c>
+      <c r="B319" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A320" t="s">
+        <v>234</v>
+      </c>
+      <c r="B320" t="s">
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -3887,23 +4044,23 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B3" s="3">
         <v>988</v>
@@ -3911,7 +4068,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B4" s="3">
         <v>988</v>
@@ -3919,258 +4076,258 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -4190,21 +4347,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="B1" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="B2" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C2" s="4">
         <v>988</v>
@@ -4212,46 +4369,46 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="B3" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="B5" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>

--- a/attendance_raw.xlsx
+++ b/attendance_raw.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RegieSapico\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1926A30-E373-472F-B091-C41AFDE4E7EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{818E2D59-9A0D-4D2F-831E-E604D02D731C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3405" yWindow="1095" windowWidth="23970" windowHeight="13695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31365" yWindow="1860" windowWidth="21015" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="supervisor-program" sheetId="2" r:id="rId1"/>
-    <sheet name="access" sheetId="4" r:id="rId2"/>
+    <sheet name="credentials" sheetId="7" r:id="rId2"/>
+    <sheet name="access" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'supervisor-program'!$A$1:$C$314</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'supervisor-program'!$A$1:$C$301</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="368">
   <si>
     <t>Agyeman, Basheera</t>
   </si>
@@ -174,15 +175,9 @@
     <t>Felix, Edna</t>
   </si>
   <si>
-    <t>Forman, Jack</t>
-  </si>
-  <si>
     <t>Fusaro, Jessica</t>
   </si>
   <si>
-    <t>Gagnon, Jaime</t>
-  </si>
-  <si>
     <t>Garcia, America</t>
   </si>
   <si>
@@ -249,9 +244,6 @@
     <t>Lines, Jaclyn</t>
   </si>
   <si>
-    <t>Lloyd, Cheyenne</t>
-  </si>
-  <si>
     <t>Lozano, Holly</t>
   </si>
   <si>
@@ -420,9 +412,6 @@
     <t>Allen, Will</t>
   </si>
   <si>
-    <t>Arnhold, Charlyn</t>
-  </si>
-  <si>
     <t>Arnold, Beckett</t>
   </si>
   <si>
@@ -528,9 +517,6 @@
     <t>Ullah, Nasima</t>
   </si>
   <si>
-    <t>Wegener, Corinne</t>
-  </si>
-  <si>
     <t>Amin, Layla</t>
   </si>
   <si>
@@ -597,18 +583,12 @@
     <t>Oliphant, Dan</t>
   </si>
   <si>
-    <t>Stumpf, Abygahle</t>
-  </si>
-  <si>
     <t>Sykes, Laquanna</t>
   </si>
   <si>
     <t>Tareen, Mahnoor</t>
   </si>
   <si>
-    <t>Thompson, Veronica</t>
-  </si>
-  <si>
     <t>Witczak, Cynthia</t>
   </si>
   <si>
@@ -645,9 +625,6 @@
     <t>Koh, Jinny</t>
   </si>
   <si>
-    <t>Livingston, Anna</t>
-  </si>
-  <si>
     <t>Markowitz, David</t>
   </si>
   <si>
@@ -675,9 +652,6 @@
     <t>Jamieson, Harry</t>
   </si>
   <si>
-    <t>Galante, Jessica</t>
-  </si>
-  <si>
     <t>Stanley, Chase</t>
   </si>
   <si>
@@ -831,9 +805,6 @@
     <t>Frye, Angela</t>
   </si>
   <si>
-    <t>Matundan, Geneveve</t>
-  </si>
-  <si>
     <t>Gainer, Jazmine</t>
   </si>
   <si>
@@ -876,18 +847,12 @@
     <t>Phinn, Jade</t>
   </si>
   <si>
-    <t>Phoenix, Hazel</t>
-  </si>
-  <si>
     <t>Ratchford, Viktoria</t>
   </si>
   <si>
     <t>Reynolds, Chelsea</t>
   </si>
   <si>
-    <t>Ross, Tracie</t>
-  </si>
-  <si>
     <t>Sagon, Chanell</t>
   </si>
   <si>
@@ -924,9 +889,6 @@
     <t>Abdalla, Salma</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Ames, Sumner</t>
   </si>
   <si>
@@ -1050,17 +1012,143 @@
     <t>Williams, TreVaunte</t>
   </si>
   <si>
-    <t>Zaragoza, Sharon</t>
-  </si>
-  <si>
     <t>TeenLink</t>
+  </si>
+  <si>
+    <t>Lloyd, Cheyene</t>
+  </si>
+  <si>
+    <t>tbass@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>snewberry@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>thyndman@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>kgreen@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>nhammad@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>bquiroz@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>tguzikowski@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>aparks@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>cpyott@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>ahalliwell@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>nbogdas@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>aloch@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>hopoku@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>mpastores@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>mprice@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>jroberts@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>mzeitler@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>jhouse@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>MChrzanowski@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>kkrause@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>sabraham@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>wsusilo@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>nsmith@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>kvelasquez@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>kschutz@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>kraker@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>kbjorn@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>afrye@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>asipple@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>APishue@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>ndavis@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>smaple@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>rsapico@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>acampbell@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>dgoodman@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>sayers@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>clevitan@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>ajackson@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>jjamieson@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>csagon@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>lgroh@crisisconnections.org</t>
+  </si>
+  <si>
+    <t>KGardiner@crisisconnections.org</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Verdana"/>
@@ -1076,6 +1164,12 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="Verdana"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Verdana"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1104,7 +1198,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1115,6 +1209,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1489,7 +1586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5807181E-856C-4C1B-8B3E-AC1CE6A3DC63}">
-  <dimension ref="A1:C314"/>
+  <dimension ref="A1:C301"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.3984375" bestFit="1" customWidth="1"/>
@@ -1499,21 +1596,21 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="B2" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="C2" s="5">
         <v>988</v>
@@ -1524,7 +1621,7 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="C3" s="5">
         <v>988</v>
@@ -1535,7 +1632,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="C4" s="5">
         <v>988</v>
@@ -1546,21 +1643,21 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B6" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -1568,7 +1665,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="C7" s="5">
         <v>988</v>
@@ -1579,7 +1676,7 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="C8" s="5">
         <v>988</v>
@@ -1587,10 +1684,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="B9" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="C9" s="5">
         <v>988</v>
@@ -1598,13 +1695,13 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B10" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -1612,7 +1709,7 @@
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="C11" s="5">
         <v>988</v>
@@ -1620,120 +1717,120 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="B12" t="s">
-        <v>224</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>291</v>
+        <v>149</v>
+      </c>
+      <c r="C12" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>316</v>
+        <v>303</v>
       </c>
       <c r="B13" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B14" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>128</v>
+        <v>202</v>
       </c>
       <c r="B15" t="s">
-        <v>227</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>289</v>
+        <v>214</v>
+      </c>
+      <c r="C15" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>210</v>
+        <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>223</v>
-      </c>
-      <c r="C16" s="5">
-        <v>988</v>
+        <v>222</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>125</v>
       </c>
       <c r="B18" t="s">
-        <v>232</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>292</v>
+        <v>224</v>
+      </c>
+      <c r="C18" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>129</v>
+        <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>233</v>
-      </c>
-      <c r="C19" s="5">
-        <v>988</v>
+        <v>225</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>8</v>
+        <v>226</v>
       </c>
       <c r="B20" t="s">
-        <v>234</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>289</v>
+        <v>287</v>
+      </c>
+      <c r="C20" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>235</v>
+        <v>9</v>
       </c>
       <c r="B21" t="s">
-        <v>300</v>
-      </c>
-      <c r="C21" s="5" t="e">
-        <v>#N/A</v>
+        <v>211</v>
+      </c>
+      <c r="C21" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C22" s="5">
         <v>988</v>
@@ -1741,32 +1838,32 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>10</v>
+        <v>160</v>
       </c>
       <c r="B23" t="s">
-        <v>236</v>
-      </c>
-      <c r="C23" s="5">
-        <v>988</v>
+        <v>228</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>165</v>
+        <v>229</v>
       </c>
       <c r="B24" t="s">
-        <v>237</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>291</v>
+        <v>230</v>
+      </c>
+      <c r="C24" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>238</v>
+        <v>161</v>
       </c>
       <c r="B25" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="C25" s="5">
         <v>988</v>
@@ -1774,10 +1871,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>166</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C26" s="5">
         <v>988</v>
@@ -1785,142 +1882,142 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>240</v>
-      </c>
-      <c r="C27" s="5">
-        <v>988</v>
+        <v>232</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>304</v>
       </c>
       <c r="B28" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>317</v>
+        <v>13</v>
       </c>
       <c r="B29" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>13</v>
+        <v>235</v>
       </c>
       <c r="B30" t="s">
-        <v>243</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>291</v>
+        <v>219</v>
+      </c>
+      <c r="C30" s="5">
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>244</v>
+        <v>126</v>
       </c>
       <c r="B31" t="s">
-        <v>228</v>
-      </c>
-      <c r="C31" s="5" t="e">
-        <v>#N/A</v>
+        <v>149</v>
+      </c>
+      <c r="C31" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B32" t="s">
-        <v>153</v>
-      </c>
-      <c r="C32" s="5">
-        <v>988</v>
+        <v>213</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>131</v>
+        <v>236</v>
       </c>
       <c r="B33" t="s">
-        <v>222</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>289</v>
+        <v>287</v>
+      </c>
+      <c r="C33" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>245</v>
+        <v>14</v>
       </c>
       <c r="B34" t="s">
-        <v>300</v>
-      </c>
-      <c r="C34" s="5" t="e">
-        <v>#N/A</v>
+        <v>216</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B35" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B36" t="s">
-        <v>222</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>289</v>
+        <v>237</v>
+      </c>
+      <c r="C36" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>16</v>
+        <v>162</v>
       </c>
       <c r="B37" t="s">
-        <v>246</v>
-      </c>
-      <c r="C37" s="5">
-        <v>988</v>
+        <v>234</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>167</v>
+        <v>238</v>
       </c>
       <c r="B38" t="s">
-        <v>243</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>291</v>
+        <v>239</v>
+      </c>
+      <c r="C38" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>247</v>
+        <v>17</v>
       </c>
       <c r="B39" t="s">
-        <v>248</v>
+        <v>226</v>
       </c>
       <c r="C39" s="5">
         <v>988</v>
@@ -1928,10 +2025,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>17</v>
+        <v>284</v>
       </c>
       <c r="B40" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C40" s="5">
         <v>988</v>
@@ -1939,65 +2036,65 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>297</v>
+        <v>18</v>
       </c>
       <c r="B41" t="s">
-        <v>246</v>
-      </c>
-      <c r="C41" s="5">
-        <v>988</v>
+        <v>234</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B42" t="s">
-        <v>243</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>291</v>
+        <v>227</v>
+      </c>
+      <c r="C42" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B43" t="s">
-        <v>236</v>
-      </c>
-      <c r="C43" s="5">
-        <v>988</v>
+        <v>225</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B44" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>21</v>
+        <v>128</v>
       </c>
       <c r="B45" t="s">
-        <v>241</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>289</v>
+        <v>227</v>
+      </c>
+      <c r="C45" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>132</v>
+        <v>22</v>
       </c>
       <c r="B46" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="C46" s="5">
         <v>988</v>
@@ -2005,10 +2102,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>22</v>
+        <v>186</v>
       </c>
       <c r="B47" t="s">
-        <v>235</v>
+        <v>149</v>
       </c>
       <c r="C47" s="5">
         <v>988</v>
@@ -2016,65 +2113,65 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>193</v>
+        <v>221</v>
       </c>
       <c r="B48" t="s">
-        <v>153</v>
+        <v>240</v>
       </c>
       <c r="C48" s="5">
-        <v>988</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>230</v>
+        <v>23</v>
       </c>
       <c r="B49" t="s">
-        <v>249</v>
-      </c>
-      <c r="C49" s="5" t="e">
-        <v>#N/A</v>
+        <v>222</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>23</v>
+        <v>129</v>
       </c>
       <c r="B50" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>133</v>
+        <v>24</v>
       </c>
       <c r="B51" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>292</v>
+        <v>279</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B52" t="s">
-        <v>237</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>291</v>
+        <v>226</v>
+      </c>
+      <c r="C52" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>25</v>
+        <v>163</v>
       </c>
       <c r="B53" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
       <c r="C53" s="5">
         <v>988</v>
@@ -2082,10 +2179,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>168</v>
+        <v>241</v>
       </c>
       <c r="B54" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C54" s="5">
         <v>988</v>
@@ -2093,43 +2190,43 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>250</v>
+        <v>187</v>
       </c>
       <c r="B55" t="s">
-        <v>235</v>
-      </c>
-      <c r="C55" s="5">
-        <v>988</v>
+        <v>225</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="B56" t="s">
-        <v>234</v>
+        <v>209</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>225</v>
+        <v>26</v>
       </c>
       <c r="B57" t="s">
-        <v>218</v>
-      </c>
-      <c r="C57" s="5" t="e">
-        <v>#N/A</v>
+        <v>237</v>
+      </c>
+      <c r="C57" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>26</v>
+        <v>164</v>
       </c>
       <c r="B58" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="C58" s="5">
         <v>988</v>
@@ -2137,10 +2234,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B59" t="s">
-        <v>248</v>
+        <v>226</v>
       </c>
       <c r="C59" s="5">
         <v>988</v>
@@ -2148,32 +2245,32 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>170</v>
+        <v>27</v>
       </c>
       <c r="B60" t="s">
-        <v>235</v>
-      </c>
-      <c r="C60" s="5">
-        <v>988</v>
+        <v>242</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B61" t="s">
-        <v>251</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>289</v>
+        <v>214</v>
+      </c>
+      <c r="C61" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B62" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="C62" s="5">
         <v>988</v>
@@ -2181,175 +2278,175 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B63" t="s">
-        <v>220</v>
-      </c>
-      <c r="C63" s="5">
-        <v>988</v>
+        <v>208</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>30</v>
+        <v>130</v>
       </c>
       <c r="B64" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>134</v>
+        <v>188</v>
       </c>
       <c r="B65" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="B66" t="s">
-        <v>253</v>
+        <v>208</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>196</v>
+        <v>31</v>
       </c>
       <c r="B67" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>31</v>
+        <v>245</v>
       </c>
       <c r="B68" t="s">
-        <v>218</v>
-      </c>
-      <c r="C68" s="5" t="e">
-        <v>#N/A</v>
+        <v>287</v>
+      </c>
+      <c r="C68" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="B69" t="s">
-        <v>300</v>
-      </c>
-      <c r="C69" s="5" t="e">
-        <v>#N/A</v>
+        <v>235</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B70" t="s">
-        <v>244</v>
-      </c>
-      <c r="C70" s="5" t="e">
-        <v>#N/A</v>
+        <v>209</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>256</v>
+        <v>131</v>
       </c>
       <c r="B71" t="s">
-        <v>218</v>
-      </c>
-      <c r="C71" s="5" t="e">
-        <v>#N/A</v>
+        <v>248</v>
+      </c>
+      <c r="C71" s="5">
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>135</v>
+        <v>248</v>
       </c>
       <c r="B72" t="s">
-        <v>257</v>
-      </c>
-      <c r="C72" s="5" t="e">
-        <v>#N/A</v>
+        <v>287</v>
+      </c>
+      <c r="C72" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>257</v>
+        <v>205</v>
       </c>
       <c r="B73" t="s">
-        <v>300</v>
-      </c>
-      <c r="C73" s="5" t="e">
-        <v>#N/A</v>
+        <v>227</v>
+      </c>
+      <c r="C73" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>214</v>
+        <v>190</v>
       </c>
       <c r="B74" t="s">
-        <v>236</v>
-      </c>
-      <c r="C74" s="5">
-        <v>988</v>
+        <v>218</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>197</v>
+        <v>249</v>
       </c>
       <c r="B75" t="s">
-        <v>227</v>
-      </c>
-      <c r="C75" s="5" t="s">
-        <v>289</v>
+        <v>219</v>
+      </c>
+      <c r="C75" s="5">
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>258</v>
+        <v>32</v>
       </c>
       <c r="B76" t="s">
-        <v>228</v>
-      </c>
-      <c r="C76" s="5" t="e">
-        <v>#N/A</v>
+        <v>243</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B77" t="s">
-        <v>252</v>
-      </c>
-      <c r="C77" s="5" t="s">
-        <v>289</v>
+        <v>226</v>
+      </c>
+      <c r="C77" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>33</v>
+        <v>166</v>
       </c>
       <c r="B78" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
       <c r="C78" s="5">
         <v>988</v>
@@ -2357,164 +2454,164 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>171</v>
+        <v>34</v>
       </c>
       <c r="B79" t="s">
         <v>223</v>
       </c>
-      <c r="C79" s="5">
-        <v>988</v>
+      <c r="C79" s="5" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B80" t="s">
-        <v>232</v>
-      </c>
-      <c r="C80" s="5" t="s">
-        <v>292</v>
+        <v>236</v>
+      </c>
+      <c r="C80" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B81" t="s">
-        <v>245</v>
-      </c>
-      <c r="C81" s="5">
-        <v>988</v>
+        <v>212</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B82" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B83" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>38</v>
+        <v>305</v>
       </c>
       <c r="B84" t="s">
-        <v>222</v>
-      </c>
-      <c r="C84" s="5" t="s">
-        <v>289</v>
+        <v>239</v>
+      </c>
+      <c r="C84" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>318</v>
+        <v>132</v>
       </c>
       <c r="B85" t="s">
-        <v>248</v>
-      </c>
-      <c r="C85" s="5" t="e">
-        <v>#N/A</v>
+        <v>211</v>
+      </c>
+      <c r="C85" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>136</v>
+        <v>39</v>
       </c>
       <c r="B86" t="s">
-        <v>220</v>
-      </c>
-      <c r="C86" s="5">
-        <v>988</v>
+        <v>234</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>39</v>
+        <v>306</v>
       </c>
       <c r="B87" t="s">
-        <v>243</v>
-      </c>
-      <c r="C87" s="5" t="s">
-        <v>291</v>
+        <v>258</v>
+      </c>
+      <c r="C87" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="B88" t="s">
-        <v>268</v>
-      </c>
-      <c r="C88" s="5" t="e">
-        <v>#N/A</v>
+        <v>239</v>
+      </c>
+      <c r="C88" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>320</v>
+        <v>133</v>
       </c>
       <c r="B89" t="s">
-        <v>295</v>
-      </c>
-      <c r="C89" s="5" t="e">
-        <v>#N/A</v>
+        <v>231</v>
+      </c>
+      <c r="C89" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>137</v>
+        <v>40</v>
       </c>
       <c r="B90" t="s">
-        <v>240</v>
-      </c>
-      <c r="C90" s="5">
-        <v>988</v>
+        <v>208</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B91" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B92" t="s">
-        <v>222</v>
-      </c>
-      <c r="C92" s="5" t="s">
-        <v>289</v>
+        <v>230</v>
+      </c>
+      <c r="C92" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B93" t="s">
-        <v>239</v>
+        <v>210</v>
       </c>
       <c r="C93" s="5">
         <v>988</v>
@@ -2522,32 +2619,32 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>43</v>
+        <v>250</v>
       </c>
       <c r="B94" t="s">
-        <v>219</v>
-      </c>
-      <c r="C94" s="5">
-        <v>988</v>
+        <v>209</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>259</v>
+        <v>44</v>
       </c>
       <c r="B95" t="s">
-        <v>218</v>
-      </c>
-      <c r="C95" s="5" t="s">
-        <v>289</v>
+        <v>211</v>
+      </c>
+      <c r="C95" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>44</v>
+        <v>251</v>
       </c>
       <c r="B96" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C96" s="5">
         <v>988</v>
@@ -2555,10 +2652,10 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>260</v>
+        <v>134</v>
       </c>
       <c r="B97" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C97" s="5">
         <v>988</v>
@@ -2566,109 +2663,109 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>138</v>
+        <v>252</v>
       </c>
       <c r="B98" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="C98" s="5">
-        <v>988</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>45</v>
+        <v>254</v>
       </c>
       <c r="B99" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>261</v>
+        <v>45</v>
       </c>
       <c r="B100" t="s">
-        <v>262</v>
-      </c>
-      <c r="C100" s="5" t="e">
-        <v>#N/A</v>
+        <v>244</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>263</v>
+        <v>167</v>
       </c>
       <c r="B101" t="s">
-        <v>244</v>
-      </c>
-      <c r="C101" s="5" t="e">
-        <v>#N/A</v>
+        <v>225</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>46</v>
+        <v>255</v>
       </c>
       <c r="B102" t="s">
-        <v>253</v>
-      </c>
-      <c r="C102" s="5" t="s">
-        <v>289</v>
+        <v>210</v>
+      </c>
+      <c r="C102" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>172</v>
+        <v>256</v>
       </c>
       <c r="B103" t="s">
-        <v>234</v>
-      </c>
-      <c r="C103" s="5" t="s">
-        <v>289</v>
+        <v>236</v>
+      </c>
+      <c r="C103" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>47</v>
+        <v>308</v>
       </c>
       <c r="B104" t="s">
-        <v>264</v>
-      </c>
-      <c r="C104" s="5" t="s">
-        <v>289</v>
+        <v>211</v>
+      </c>
+      <c r="C104" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>265</v>
+        <v>135</v>
       </c>
       <c r="B105" t="s">
-        <v>219</v>
-      </c>
-      <c r="C105" s="5">
-        <v>988</v>
+        <v>242</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>212</v>
+        <v>46</v>
       </c>
       <c r="B106" t="s">
-        <v>264</v>
-      </c>
-      <c r="C106" s="5" t="s">
-        <v>289</v>
+        <v>227</v>
+      </c>
+      <c r="C106" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>266</v>
+        <v>191</v>
       </c>
       <c r="B107" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="C107" s="5">
         <v>988</v>
@@ -2676,32 +2773,32 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>321</v>
+        <v>219</v>
       </c>
       <c r="B108" t="s">
         <v>220</v>
       </c>
       <c r="C108" s="5">
-        <v>988</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B109" t="s">
-        <v>251</v>
-      </c>
-      <c r="C109" s="5" t="s">
-        <v>289</v>
+        <v>210</v>
+      </c>
+      <c r="C109" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>48</v>
+        <v>257</v>
       </c>
       <c r="B110" t="s">
-        <v>236</v>
+        <v>287</v>
       </c>
       <c r="C110" s="5">
         <v>988</v>
@@ -2709,10 +2806,10 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>198</v>
+        <v>168</v>
       </c>
       <c r="B111" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
       <c r="C111" s="5">
         <v>988</v>
@@ -2720,21 +2817,21 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>228</v>
+        <v>47</v>
       </c>
       <c r="B112" t="s">
-        <v>229</v>
-      </c>
-      <c r="C112" s="5" t="e">
-        <v>#N/A</v>
+        <v>211</v>
+      </c>
+      <c r="C112" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>140</v>
+        <v>309</v>
       </c>
       <c r="B113" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="C113" s="5">
         <v>988</v>
@@ -2742,32 +2839,32 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>267</v>
+        <v>240</v>
       </c>
       <c r="B114" t="s">
-        <v>300</v>
-      </c>
-      <c r="C114" s="5" t="e">
-        <v>#N/A</v>
+        <v>259</v>
+      </c>
+      <c r="C114" s="5">
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="B115" t="s">
-        <v>268</v>
-      </c>
-      <c r="C115" s="5">
-        <v>988</v>
+        <v>242</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>49</v>
+        <v>214</v>
       </c>
       <c r="B116" t="s">
-        <v>220</v>
+        <v>287</v>
       </c>
       <c r="C116" s="5">
         <v>988</v>
@@ -2775,10 +2872,10 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>322</v>
+        <v>169</v>
       </c>
       <c r="B117" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="C117" s="5">
         <v>988</v>
@@ -2786,43 +2883,43 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>249</v>
+        <v>224</v>
       </c>
       <c r="B118" t="s">
-        <v>269</v>
-      </c>
-      <c r="C118" s="5" t="e">
-        <v>#N/A</v>
+        <v>287</v>
+      </c>
+      <c r="C118" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>199</v>
+        <v>137</v>
       </c>
       <c r="B119" t="s">
-        <v>251</v>
-      </c>
-      <c r="C119" s="5" t="s">
-        <v>289</v>
+        <v>239</v>
+      </c>
+      <c r="C119" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>223</v>
+        <v>260</v>
       </c>
       <c r="B120" t="s">
-        <v>300</v>
-      </c>
-      <c r="C120" s="5" t="e">
-        <v>#N/A</v>
+        <v>230</v>
+      </c>
+      <c r="C120" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>174</v>
+        <v>237</v>
       </c>
       <c r="B121" t="s">
-        <v>233</v>
+        <v>287</v>
       </c>
       <c r="C121" s="5">
         <v>988</v>
@@ -2830,21 +2927,21 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>233</v>
+        <v>138</v>
       </c>
       <c r="B122" t="s">
-        <v>300</v>
-      </c>
-      <c r="C122" s="5" t="e">
-        <v>#N/A</v>
+        <v>231</v>
+      </c>
+      <c r="C122" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>141</v>
+        <v>230</v>
       </c>
       <c r="B123" t="s">
-        <v>248</v>
+        <v>287</v>
       </c>
       <c r="C123" s="5">
         <v>988</v>
@@ -2852,32 +2949,32 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>270</v>
+        <v>48</v>
       </c>
       <c r="B124" t="s">
-        <v>239</v>
-      </c>
-      <c r="C124" s="5">
-        <v>988</v>
+        <v>228</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="B125" t="s">
-        <v>300</v>
-      </c>
-      <c r="C125" s="5" t="e">
-        <v>#N/A</v>
+        <v>239</v>
+      </c>
+      <c r="C125" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>142</v>
+        <v>49</v>
       </c>
       <c r="B126" t="s">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="C126" s="5">
         <v>988</v>
@@ -2885,32 +2982,32 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>239</v>
+        <v>50</v>
       </c>
       <c r="B127" t="s">
-        <v>300</v>
-      </c>
-      <c r="C127" s="5" t="e">
-        <v>#N/A</v>
+        <v>232</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>50</v>
+        <v>139</v>
       </c>
       <c r="B128" t="s">
-        <v>237</v>
-      </c>
-      <c r="C128" s="5" t="s">
-        <v>291</v>
+        <v>224</v>
+      </c>
+      <c r="C128" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>271</v>
+        <v>140</v>
       </c>
       <c r="B129" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="C129" s="5">
         <v>988</v>
@@ -2923,38 +3020,38 @@
       <c r="B130" t="s">
         <v>223</v>
       </c>
-      <c r="C130" s="5">
-        <v>988</v>
+      <c r="C130" s="5" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>52</v>
+        <v>222</v>
       </c>
       <c r="B131" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>143</v>
+        <v>232</v>
       </c>
       <c r="B132" t="s">
-        <v>233</v>
-      </c>
-      <c r="C132" s="5">
-        <v>988</v>
+        <v>209</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>144</v>
+        <v>262</v>
       </c>
       <c r="B133" t="s">
-        <v>268</v>
+        <v>224</v>
       </c>
       <c r="C133" s="5">
         <v>988</v>
@@ -2962,131 +3059,131 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>53</v>
+        <v>211</v>
       </c>
       <c r="B134" t="s">
-        <v>232</v>
-      </c>
-      <c r="C134" s="5" t="s">
-        <v>292</v>
+        <v>287</v>
+      </c>
+      <c r="C134" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>231</v>
+        <v>52</v>
       </c>
       <c r="B135" t="s">
-        <v>218</v>
-      </c>
-      <c r="C135" s="5" t="e">
-        <v>#N/A</v>
+        <v>237</v>
+      </c>
+      <c r="C135" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>241</v>
+        <v>53</v>
       </c>
       <c r="B136" t="s">
-        <v>218</v>
-      </c>
-      <c r="C136" s="5" t="e">
-        <v>#N/A</v>
+        <v>239</v>
+      </c>
+      <c r="C136" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>272</v>
+        <v>54</v>
       </c>
       <c r="B137" t="s">
-        <v>233</v>
-      </c>
-      <c r="C137" s="5">
-        <v>988</v>
+        <v>218</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>220</v>
+        <v>170</v>
       </c>
       <c r="B138" t="s">
-        <v>300</v>
-      </c>
-      <c r="C138" s="5" t="e">
-        <v>#N/A</v>
+        <v>216</v>
+      </c>
+      <c r="C138" s="5" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>54</v>
+        <v>171</v>
       </c>
       <c r="B139" t="s">
-        <v>246</v>
-      </c>
-      <c r="C139" s="5">
-        <v>988</v>
+        <v>244</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>55</v>
+        <v>203</v>
       </c>
       <c r="B140" t="s">
-        <v>248</v>
-      </c>
-      <c r="C140" s="5">
-        <v>988</v>
+        <v>232</v>
+      </c>
+      <c r="C140" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>56</v>
+        <v>172</v>
       </c>
       <c r="B141" t="s">
-        <v>227</v>
-      </c>
-      <c r="C141" s="5" t="s">
-        <v>289</v>
+        <v>149</v>
+      </c>
+      <c r="C141" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>175</v>
+        <v>55</v>
       </c>
       <c r="B142" t="s">
-        <v>225</v>
-      </c>
-      <c r="C142" s="5" t="s">
-        <v>338</v>
+        <v>237</v>
+      </c>
+      <c r="C142" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>176</v>
+        <v>285</v>
       </c>
       <c r="B143" t="s">
-        <v>253</v>
-      </c>
-      <c r="C143" s="5" t="s">
-        <v>289</v>
+        <v>231</v>
+      </c>
+      <c r="C143" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>211</v>
+        <v>56</v>
       </c>
       <c r="B144" t="s">
-        <v>241</v>
-      </c>
-      <c r="C144" s="5" t="s">
-        <v>289</v>
+        <v>236</v>
+      </c>
+      <c r="C144" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>177</v>
+        <v>57</v>
       </c>
       <c r="B145" t="s">
-        <v>153</v>
+        <v>211</v>
       </c>
       <c r="C145" s="5">
         <v>988</v>
@@ -3094,101 +3191,101 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B146" t="s">
-        <v>257</v>
-      </c>
-      <c r="C146" s="5" t="e">
-        <v>#N/A</v>
+        <v>244</v>
+      </c>
+      <c r="C146" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>298</v>
+        <v>59</v>
       </c>
       <c r="B147" t="s">
-        <v>240</v>
-      </c>
-      <c r="C147" s="5">
-        <v>988</v>
+        <v>225</v>
+      </c>
+      <c r="C147" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>58</v>
+        <v>173</v>
       </c>
       <c r="B148" t="s">
-        <v>245</v>
-      </c>
-      <c r="C148" s="5">
-        <v>988</v>
+        <v>225</v>
+      </c>
+      <c r="C148" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>59</v>
+        <v>310</v>
       </c>
       <c r="B149" t="s">
-        <v>220</v>
-      </c>
-      <c r="C149" s="5">
-        <v>988</v>
+        <v>223</v>
+      </c>
+      <c r="C149" s="5" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>60</v>
+        <v>263</v>
       </c>
       <c r="B150" t="s">
-        <v>253</v>
-      </c>
-      <c r="C150" s="5" t="s">
-        <v>289</v>
+        <v>287</v>
+      </c>
+      <c r="C150" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B151" t="s">
-        <v>234</v>
-      </c>
-      <c r="C151" s="5" t="s">
-        <v>289</v>
+        <v>214</v>
+      </c>
+      <c r="C151" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>178</v>
+        <v>141</v>
       </c>
       <c r="B152" t="s">
-        <v>234</v>
+        <v>215</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>323</v>
+        <v>286</v>
       </c>
       <c r="B153" t="s">
-        <v>232</v>
-      </c>
-      <c r="C153" s="5" t="s">
-        <v>292</v>
+        <v>227</v>
+      </c>
+      <c r="C153" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>273</v>
+        <v>61</v>
       </c>
       <c r="B154" t="s">
-        <v>300</v>
-      </c>
-      <c r="C154" s="5" t="e">
-        <v>#N/A</v>
+        <v>149</v>
+      </c>
+      <c r="C154" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.2">
@@ -3196,29 +3293,29 @@
         <v>62</v>
       </c>
       <c r="B155" t="s">
-        <v>223</v>
-      </c>
-      <c r="C155" s="5">
-        <v>988</v>
+        <v>208</v>
+      </c>
+      <c r="C155" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>145</v>
+        <v>264</v>
       </c>
       <c r="B156" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>299</v>
+        <v>63</v>
       </c>
       <c r="B157" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="C157" s="5">
         <v>988</v>
@@ -3226,164 +3323,164 @@
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B158" t="s">
-        <v>153</v>
-      </c>
-      <c r="C158" s="5">
-        <v>988</v>
+        <v>213</v>
+      </c>
+      <c r="C158" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>64</v>
+        <v>193</v>
       </c>
       <c r="B159" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>274</v>
+        <v>194</v>
       </c>
       <c r="B160" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>65</v>
+        <v>242</v>
       </c>
       <c r="B161" t="s">
-        <v>223</v>
-      </c>
-      <c r="C161" s="5">
-        <v>988</v>
+        <v>209</v>
+      </c>
+      <c r="C161" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B162" t="s">
-        <v>222</v>
-      </c>
-      <c r="C162" s="5" t="s">
-        <v>289</v>
+        <v>226</v>
+      </c>
+      <c r="C162" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="B163" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>201</v>
+        <v>175</v>
       </c>
       <c r="B164" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>251</v>
+        <v>176</v>
       </c>
       <c r="B165" t="s">
-        <v>218</v>
-      </c>
-      <c r="C165" s="5" t="e">
-        <v>#N/A</v>
+        <v>232</v>
+      </c>
+      <c r="C165" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B166" t="s">
-        <v>235</v>
-      </c>
-      <c r="C166" s="5">
-        <v>988</v>
+        <v>225</v>
+      </c>
+      <c r="C166" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>179</v>
+        <v>287</v>
       </c>
       <c r="B167" t="s">
-        <v>226</v>
-      </c>
-      <c r="C167" s="5" t="s">
-        <v>289</v>
+        <v>219</v>
+      </c>
+      <c r="C167" s="5">
+        <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>180</v>
+        <v>311</v>
       </c>
       <c r="B168" t="s">
-        <v>253</v>
-      </c>
-      <c r="C168" s="5" t="s">
-        <v>289</v>
+        <v>258</v>
+      </c>
+      <c r="C168" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>181</v>
+        <v>67</v>
       </c>
       <c r="B169" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>68</v>
+        <v>325</v>
       </c>
       <c r="B170" t="s">
-        <v>234</v>
-      </c>
-      <c r="C170" s="5" t="s">
-        <v>289</v>
+        <v>214</v>
+      </c>
+      <c r="C170" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>300</v>
+        <v>258</v>
       </c>
       <c r="B171" t="s">
-        <v>228</v>
-      </c>
-      <c r="C171" s="5" t="e">
-        <v>#N/A</v>
+        <v>287</v>
+      </c>
+      <c r="C171" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>324</v>
+        <v>68</v>
       </c>
       <c r="B172" t="s">
-        <v>268</v>
+        <v>231</v>
       </c>
       <c r="C172" s="5">
         <v>988</v>
@@ -3391,54 +3488,54 @@
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>69</v>
+        <v>177</v>
       </c>
       <c r="B173" t="s">
-        <v>251</v>
-      </c>
-      <c r="C173" s="5" t="s">
-        <v>289</v>
+        <v>224</v>
+      </c>
+      <c r="C173" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="B174" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>70</v>
+        <v>196</v>
       </c>
       <c r="B175" t="s">
-        <v>223</v>
-      </c>
-      <c r="C175" s="5" t="e">
-        <v>#N/A</v>
+        <v>149</v>
+      </c>
+      <c r="C175" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>268</v>
+        <v>142</v>
       </c>
       <c r="B176" t="s">
-        <v>300</v>
-      </c>
-      <c r="C176" s="5" t="e">
-        <v>#N/A</v>
+        <v>213</v>
+      </c>
+      <c r="C176" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B177" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="C177" s="5">
         <v>988</v>
@@ -3446,43 +3543,43 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>262</v>
+        <v>70</v>
       </c>
       <c r="B178" t="s">
-        <v>295</v>
-      </c>
-      <c r="C178" s="5" t="e">
-        <v>#N/A</v>
+        <v>210</v>
+      </c>
+      <c r="C178" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>182</v>
+        <v>71</v>
       </c>
       <c r="B179" t="s">
-        <v>233</v>
-      </c>
-      <c r="C179" s="5">
-        <v>988</v>
+        <v>217</v>
+      </c>
+      <c r="C179" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>203</v>
+        <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>251</v>
+        <v>222</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>204</v>
+        <v>265</v>
       </c>
       <c r="B181" t="s">
-        <v>153</v>
+        <v>226</v>
       </c>
       <c r="C181" s="5">
         <v>988</v>
@@ -3490,21 +3587,21 @@
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>146</v>
+        <v>72</v>
       </c>
       <c r="B182" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>72</v>
+        <v>312</v>
       </c>
       <c r="B183" t="s">
-        <v>268</v>
+        <v>149</v>
       </c>
       <c r="C183" s="5">
         <v>988</v>
@@ -3512,21 +3609,21 @@
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>264</v>
+        <v>73</v>
       </c>
       <c r="B184" t="s">
-        <v>218</v>
-      </c>
-      <c r="C184" s="5" t="e">
-        <v>#N/A</v>
+        <v>237</v>
+      </c>
+      <c r="C184" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>73</v>
+        <v>143</v>
       </c>
       <c r="B185" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="C185" s="5">
         <v>988</v>
@@ -3537,29 +3634,29 @@
         <v>74</v>
       </c>
       <c r="B186" t="s">
-        <v>226</v>
-      </c>
-      <c r="C186" s="5" t="s">
-        <v>289</v>
+        <v>210</v>
+      </c>
+      <c r="C186" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>183</v>
+        <v>75</v>
       </c>
       <c r="B187" t="s">
-        <v>231</v>
-      </c>
-      <c r="C187" s="5" t="s">
-        <v>289</v>
+        <v>226</v>
+      </c>
+      <c r="C187" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>275</v>
+        <v>144</v>
       </c>
       <c r="B188" t="s">
-        <v>235</v>
+        <v>149</v>
       </c>
       <c r="C188" s="5">
         <v>988</v>
@@ -3567,54 +3664,54 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B189" t="s">
-        <v>227</v>
-      </c>
-      <c r="C189" s="5" t="s">
-        <v>289</v>
+        <v>236</v>
+      </c>
+      <c r="C189" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>325</v>
+        <v>77</v>
       </c>
       <c r="B190" t="s">
-        <v>153</v>
-      </c>
-      <c r="C190" s="5" t="e">
-        <v>#N/A</v>
+        <v>223</v>
+      </c>
+      <c r="C190" s="5" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>76</v>
+        <v>313</v>
       </c>
       <c r="B191" t="s">
-        <v>246</v>
-      </c>
-      <c r="C191" s="5">
-        <v>988</v>
+        <v>233</v>
+      </c>
+      <c r="C191" s="5" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B192" t="s">
-        <v>245</v>
-      </c>
-      <c r="C192" s="5">
-        <v>988</v>
+        <v>212</v>
+      </c>
+      <c r="C192" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>77</v>
+        <v>239</v>
       </c>
       <c r="B193" t="s">
-        <v>219</v>
+        <v>287</v>
       </c>
       <c r="C193" s="5">
         <v>988</v>
@@ -3622,10 +3719,10 @@
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="B194" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="C194" s="5">
         <v>988</v>
@@ -3633,10 +3730,10 @@
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>148</v>
+        <v>288</v>
       </c>
       <c r="B195" t="s">
-        <v>153</v>
+        <v>230</v>
       </c>
       <c r="C195" s="5">
         <v>988</v>
@@ -3644,10 +3741,10 @@
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>79</v>
+        <v>266</v>
       </c>
       <c r="B196" t="s">
-        <v>245</v>
+        <v>214</v>
       </c>
       <c r="C196" s="5">
         <v>988</v>
@@ -3655,65 +3752,65 @@
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B197" t="s">
-        <v>232</v>
-      </c>
-      <c r="C197" s="5" t="s">
-        <v>292</v>
+        <v>237</v>
+      </c>
+      <c r="C197" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="B198" t="s">
-        <v>242</v>
+        <v>212</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>149</v>
+        <v>79</v>
       </c>
       <c r="B199" t="s">
-        <v>221</v>
-      </c>
-      <c r="C199" s="5" t="s">
-        <v>289</v>
+        <v>211</v>
+      </c>
+      <c r="C199" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>248</v>
+        <v>146</v>
       </c>
       <c r="B200" t="s">
-        <v>300</v>
-      </c>
-      <c r="C200" s="5" t="e">
-        <v>#N/A</v>
+        <v>223</v>
+      </c>
+      <c r="C200" s="5" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B201" t="s">
-        <v>233</v>
-      </c>
-      <c r="C201" s="5">
-        <v>988</v>
+        <v>242</v>
+      </c>
+      <c r="C201" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>301</v>
+        <v>267</v>
       </c>
       <c r="B202" t="s">
-        <v>239</v>
+        <v>287</v>
       </c>
       <c r="C202" s="5">
         <v>988</v>
@@ -3721,13 +3818,13 @@
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>276</v>
+        <v>80</v>
       </c>
       <c r="B203" t="s">
-        <v>223</v>
-      </c>
-      <c r="C203" s="5">
-        <v>988</v>
+        <v>212</v>
+      </c>
+      <c r="C203" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.2">
@@ -3735,21 +3832,21 @@
         <v>81</v>
       </c>
       <c r="B204" t="s">
-        <v>246</v>
-      </c>
-      <c r="C204" s="5">
-        <v>988</v>
+        <v>232</v>
+      </c>
+      <c r="C204" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>327</v>
+        <v>197</v>
       </c>
       <c r="B205" t="s">
-        <v>295</v>
-      </c>
-      <c r="C205" s="5" t="e">
-        <v>#N/A</v>
+        <v>226</v>
+      </c>
+      <c r="C205" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.2">
@@ -3757,73 +3854,73 @@
         <v>82</v>
       </c>
       <c r="B206" t="s">
-        <v>220</v>
-      </c>
-      <c r="C206" s="5">
-        <v>988</v>
+        <v>244</v>
+      </c>
+      <c r="C206" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>150</v>
+        <v>83</v>
       </c>
       <c r="B207" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>185</v>
+        <v>227</v>
       </c>
       <c r="B208" t="s">
-        <v>251</v>
-      </c>
-      <c r="C208" s="5" t="s">
-        <v>289</v>
+        <v>287</v>
+      </c>
+      <c r="C208" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>277</v>
+        <v>84</v>
       </c>
       <c r="B209" t="s">
-        <v>300</v>
-      </c>
-      <c r="C209" s="5" t="e">
-        <v>#N/A</v>
+        <v>213</v>
+      </c>
+      <c r="C209" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>83</v>
+        <v>212</v>
       </c>
       <c r="B210" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>84</v>
+        <v>147</v>
       </c>
       <c r="B211" t="s">
-        <v>241</v>
+        <v>213</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
-        <v>205</v>
+        <v>315</v>
       </c>
       <c r="B212" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="C212" s="5">
         <v>988</v>
@@ -3831,87 +3928,87 @@
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>85</v>
+        <v>198</v>
       </c>
       <c r="B213" t="s">
-        <v>253</v>
-      </c>
-      <c r="C213" s="5" t="s">
-        <v>289</v>
+        <v>258</v>
+      </c>
+      <c r="C213" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B214" t="s">
-        <v>221</v>
-      </c>
-      <c r="C214" s="5" t="s">
-        <v>289</v>
+        <v>210</v>
+      </c>
+      <c r="C214" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>236</v>
+        <v>268</v>
       </c>
       <c r="B215" t="s">
-        <v>300</v>
-      </c>
-      <c r="C215" s="5" t="e">
-        <v>#N/A</v>
+        <v>211</v>
+      </c>
+      <c r="C215" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
-        <v>87</v>
+        <v>223</v>
       </c>
       <c r="B216" t="s">
-        <v>222</v>
-      </c>
-      <c r="C216" s="5" t="s">
-        <v>289</v>
+        <v>249</v>
+      </c>
+      <c r="C216" s="5">
+        <v>0</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>221</v>
+        <v>86</v>
       </c>
       <c r="B217" t="s">
-        <v>218</v>
-      </c>
-      <c r="C217" s="5" t="e">
-        <v>#N/A</v>
+        <v>227</v>
+      </c>
+      <c r="C217" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
-        <v>151</v>
+        <v>87</v>
       </c>
       <c r="B218" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
-        <v>328</v>
+        <v>213</v>
       </c>
       <c r="B219" t="s">
-        <v>236</v>
-      </c>
-      <c r="C219" s="5" t="e">
-        <v>#N/A</v>
+        <v>209</v>
+      </c>
+      <c r="C219" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>206</v>
+        <v>148</v>
       </c>
       <c r="B220" t="s">
-        <v>268</v>
+        <v>214</v>
       </c>
       <c r="C220" s="5">
         <v>988</v>
@@ -3922,18 +4019,18 @@
         <v>88</v>
       </c>
       <c r="B221" t="s">
-        <v>219</v>
-      </c>
-      <c r="C221" s="5">
-        <v>988</v>
+        <v>212</v>
+      </c>
+      <c r="C221" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
-        <v>278</v>
+        <v>231</v>
       </c>
       <c r="B222" t="s">
-        <v>220</v>
+        <v>287</v>
       </c>
       <c r="C222" s="5">
         <v>988</v>
@@ -3941,32 +4038,32 @@
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
+        <v>89</v>
+      </c>
+      <c r="B223" t="s">
+        <v>234</v>
+      </c>
+      <c r="C223" s="5" t="s">
         <v>279</v>
-      </c>
-      <c r="B223" t="s">
-        <v>217</v>
-      </c>
-      <c r="C223" s="5" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
-        <v>232</v>
+        <v>149</v>
       </c>
       <c r="B224" t="s">
-        <v>258</v>
-      </c>
-      <c r="C224" s="5" t="e">
-        <v>#N/A</v>
+        <v>287</v>
+      </c>
+      <c r="C224" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B225" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="C225" s="5">
         <v>988</v>
@@ -3974,87 +4071,87 @@
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
-        <v>90</v>
+        <v>316</v>
       </c>
       <c r="B226" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B227" t="s">
-        <v>218</v>
-      </c>
-      <c r="C227" s="5" t="e">
-        <v>#N/A</v>
+        <v>235</v>
+      </c>
+      <c r="C227" s="5" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
-        <v>152</v>
+        <v>91</v>
       </c>
       <c r="B228" t="s">
         <v>223</v>
       </c>
-      <c r="C228" s="5">
-        <v>988</v>
+      <c r="C228" s="5" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B229" t="s">
-        <v>221</v>
-      </c>
-      <c r="C229" s="5" t="s">
-        <v>289</v>
+        <v>227</v>
+      </c>
+      <c r="C229" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
-        <v>240</v>
+        <v>93</v>
       </c>
       <c r="B230" t="s">
-        <v>300</v>
-      </c>
-      <c r="C230" s="5" t="e">
-        <v>#N/A</v>
+        <v>237</v>
+      </c>
+      <c r="C230" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B231" t="s">
-        <v>243</v>
-      </c>
-      <c r="C231" s="5" t="s">
-        <v>291</v>
+        <v>214</v>
+      </c>
+      <c r="C231" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
-        <v>153</v>
+        <v>269</v>
       </c>
       <c r="B232" t="s">
-        <v>300</v>
-      </c>
-      <c r="C232" s="5" t="e">
-        <v>#N/A</v>
+        <v>216</v>
+      </c>
+      <c r="C232" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
-        <v>93</v>
+        <v>150</v>
       </c>
       <c r="B233" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
       <c r="C233" s="5">
         <v>988</v>
@@ -4062,87 +4159,87 @@
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
-        <v>329</v>
+        <v>95</v>
       </c>
       <c r="B234" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
-        <v>237</v>
+        <v>151</v>
       </c>
       <c r="B235" t="s">
-        <v>244</v>
-      </c>
-      <c r="C235" s="5" t="e">
-        <v>#N/A</v>
+        <v>217</v>
+      </c>
+      <c r="C235" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
-        <v>94</v>
+        <v>317</v>
       </c>
       <c r="B236" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B237" t="s">
-        <v>236</v>
-      </c>
-      <c r="C237" s="5">
-        <v>988</v>
+        <v>223</v>
+      </c>
+      <c r="C237" s="5" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
-        <v>96</v>
+        <v>270</v>
       </c>
       <c r="B238" t="s">
-        <v>246</v>
+        <v>219</v>
       </c>
       <c r="C238" s="5">
-        <v>988</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
-        <v>97</v>
+        <v>218</v>
       </c>
       <c r="B239" t="s">
-        <v>223</v>
-      </c>
-      <c r="C239" s="5">
-        <v>988</v>
+        <v>209</v>
+      </c>
+      <c r="C239" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
-        <v>280</v>
+        <v>318</v>
       </c>
       <c r="B240" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
-        <v>154</v>
+        <v>97</v>
       </c>
       <c r="B241" t="s">
-        <v>268</v>
+        <v>231</v>
       </c>
       <c r="C241" s="5">
         <v>988</v>
@@ -4150,35 +4247,35 @@
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
-        <v>98</v>
+        <v>289</v>
       </c>
       <c r="B242" t="s">
-        <v>253</v>
-      </c>
-      <c r="C242" s="5" t="s">
-        <v>289</v>
+        <v>231</v>
+      </c>
+      <c r="C242" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
-        <v>155</v>
+        <v>271</v>
       </c>
       <c r="B243" t="s">
-        <v>226</v>
-      </c>
-      <c r="C243" s="5" t="s">
-        <v>289</v>
+        <v>219</v>
+      </c>
+      <c r="C243" s="5">
+        <v>0</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
-        <v>330</v>
+        <v>98</v>
       </c>
       <c r="B244" t="s">
-        <v>242</v>
+        <v>217</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.2">
@@ -4186,54 +4283,54 @@
         <v>99</v>
       </c>
       <c r="B245" t="s">
-        <v>232</v>
-      </c>
-      <c r="C245" s="5" t="s">
-        <v>292</v>
+        <v>258</v>
+      </c>
+      <c r="C245" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
-        <v>281</v>
+        <v>259</v>
       </c>
       <c r="B246" t="s">
-        <v>228</v>
-      </c>
-      <c r="C246" s="5" t="e">
-        <v>#N/A</v>
+        <v>253</v>
+      </c>
+      <c r="C246" s="5">
+        <v>0</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
-        <v>227</v>
+        <v>152</v>
       </c>
       <c r="B247" t="s">
-        <v>218</v>
-      </c>
-      <c r="C247" s="5" t="e">
-        <v>#N/A</v>
+        <v>225</v>
+      </c>
+      <c r="C247" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
-        <v>331</v>
+        <v>153</v>
       </c>
       <c r="B248" t="s">
-        <v>242</v>
+        <v>218</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
-        <v>282</v>
+        <v>215</v>
       </c>
       <c r="B249" t="s">
-        <v>246</v>
-      </c>
-      <c r="C249" s="5">
-        <v>988</v>
+        <v>235</v>
+      </c>
+      <c r="C249" s="5" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.2">
@@ -4241,32 +4338,32 @@
         <v>100</v>
       </c>
       <c r="B250" t="s">
-        <v>240</v>
-      </c>
-      <c r="C250" s="5">
-        <v>988</v>
+        <v>213</v>
+      </c>
+      <c r="C250" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
-        <v>302</v>
+        <v>319</v>
       </c>
       <c r="B251" t="s">
-        <v>240</v>
-      </c>
-      <c r="C251" s="5">
-        <v>988</v>
+        <v>228</v>
+      </c>
+      <c r="C251" s="5" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="B252" t="s">
-        <v>228</v>
-      </c>
-      <c r="C252" s="5" t="e">
-        <v>#N/A</v>
+        <v>237</v>
+      </c>
+      <c r="C252" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.2">
@@ -4274,18 +4371,18 @@
         <v>101</v>
       </c>
       <c r="B253" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
-        <v>102</v>
+        <v>199</v>
       </c>
       <c r="B254" t="s">
-        <v>268</v>
+        <v>210</v>
       </c>
       <c r="C254" s="5">
         <v>988</v>
@@ -4293,76 +4390,76 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
-        <v>269</v>
+        <v>200</v>
       </c>
       <c r="B255" t="s">
-        <v>262</v>
-      </c>
-      <c r="C255" s="5" t="e">
-        <v>#N/A</v>
+        <v>228</v>
+      </c>
+      <c r="C255" s="5" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
-        <v>156</v>
+        <v>320</v>
       </c>
       <c r="B256" t="s">
-        <v>234</v>
-      </c>
-      <c r="C256" s="5" t="s">
-        <v>289</v>
+        <v>231</v>
+      </c>
+      <c r="C256" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
-        <v>157</v>
+        <v>210</v>
       </c>
       <c r="B257" t="s">
-        <v>227</v>
-      </c>
-      <c r="C257" s="5" t="s">
-        <v>289</v>
+        <v>287</v>
+      </c>
+      <c r="C257" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="B258" t="s">
-        <v>244</v>
-      </c>
-      <c r="C258" s="5" t="e">
-        <v>#N/A</v>
+        <v>209</v>
+      </c>
+      <c r="C258" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="B259" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
-        <v>332</v>
+        <v>102</v>
       </c>
       <c r="B260" t="s">
-        <v>237</v>
-      </c>
-      <c r="C260" s="5" t="s">
-        <v>291</v>
+        <v>231</v>
+      </c>
+      <c r="C260" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
-        <v>284</v>
+        <v>103</v>
       </c>
       <c r="B261" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C261" s="5">
         <v>988</v>
@@ -4373,18 +4470,18 @@
         <v>104</v>
       </c>
       <c r="B262" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="C262" s="5" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
-        <v>207</v>
+        <v>155</v>
       </c>
       <c r="B263" t="s">
-        <v>219</v>
+        <v>258</v>
       </c>
       <c r="C263" s="5">
         <v>988</v>
@@ -4392,21 +4489,21 @@
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B264" t="s">
         <v>237</v>
       </c>
-      <c r="C264" s="5" t="s">
-        <v>291</v>
+      <c r="C264" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
-        <v>333</v>
+        <v>156</v>
       </c>
       <c r="B265" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="C265" s="5">
         <v>988</v>
@@ -4414,43 +4511,43 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
-        <v>219</v>
+        <v>273</v>
       </c>
       <c r="B266" t="s">
-        <v>300</v>
-      </c>
-      <c r="C266" s="5" t="e">
-        <v>#N/A</v>
+        <v>287</v>
+      </c>
+      <c r="C266" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="B267" t="s">
-        <v>218</v>
-      </c>
-      <c r="C267" s="5" t="e">
-        <v>#N/A</v>
+        <v>249</v>
+      </c>
+      <c r="C267" s="5">
+        <v>0</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="B268" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C268" s="5" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
-        <v>105</v>
+        <v>157</v>
       </c>
       <c r="B269" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C269" s="5">
         <v>988</v>
@@ -4458,32 +4555,32 @@
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
-        <v>106</v>
+        <v>243</v>
       </c>
       <c r="B270" t="s">
-        <v>245</v>
-      </c>
-      <c r="C270" s="5">
-        <v>988</v>
+        <v>209</v>
+      </c>
+      <c r="C270" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B271" t="s">
-        <v>224</v>
-      </c>
-      <c r="C271" s="5" t="s">
-        <v>291</v>
+        <v>210</v>
+      </c>
+      <c r="C271" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="B272" t="s">
-        <v>268</v>
+        <v>224</v>
       </c>
       <c r="C272" s="5">
         <v>988</v>
@@ -4491,10 +4588,10 @@
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
-        <v>213</v>
+        <v>321</v>
       </c>
       <c r="B273" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="C273" s="5">
         <v>988</v>
@@ -4502,35 +4599,35 @@
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
-        <v>160</v>
+        <v>322</v>
       </c>
       <c r="B274" t="s">
-        <v>239</v>
-      </c>
-      <c r="C274" s="5">
-        <v>988</v>
+        <v>212</v>
+      </c>
+      <c r="C274" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
-        <v>285</v>
+        <v>182</v>
       </c>
       <c r="B275" t="s">
-        <v>300</v>
-      </c>
-      <c r="C275" s="5" t="e">
-        <v>#N/A</v>
+        <v>232</v>
+      </c>
+      <c r="C275" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
-        <v>242</v>
+        <v>107</v>
       </c>
       <c r="B276" t="s">
-        <v>258</v>
-      </c>
-      <c r="C276" s="5" t="e">
-        <v>#N/A</v>
+        <v>236</v>
+      </c>
+      <c r="C276" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
@@ -4538,29 +4635,29 @@
         <v>108</v>
       </c>
       <c r="B277" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
-        <v>186</v>
+        <v>109</v>
       </c>
       <c r="B278" t="s">
-        <v>233</v>
-      </c>
-      <c r="C278" s="5">
-        <v>988</v>
+        <v>228</v>
+      </c>
+      <c r="C278" s="5" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="B279" t="s">
-        <v>245</v>
+        <v>214</v>
       </c>
       <c r="C279" s="5">
         <v>988</v>
@@ -4568,120 +4665,120 @@
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
-        <v>252</v>
+        <v>111</v>
       </c>
       <c r="B280" t="s">
-        <v>218</v>
-      </c>
-      <c r="C280" s="5" t="e">
-        <v>#N/A</v>
+        <v>237</v>
+      </c>
+      <c r="C280" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
-        <v>109</v>
+        <v>158</v>
       </c>
       <c r="B281" t="s">
-        <v>219</v>
-      </c>
-      <c r="C281" s="5">
-        <v>988</v>
+        <v>223</v>
+      </c>
+      <c r="C281" s="5" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
-        <v>187</v>
+        <v>112</v>
       </c>
       <c r="B282" t="s">
-        <v>233</v>
-      </c>
-      <c r="C282" s="5">
-        <v>988</v>
+        <v>225</v>
+      </c>
+      <c r="C282" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
-        <v>334</v>
+        <v>201</v>
       </c>
       <c r="B283" t="s">
-        <v>268</v>
-      </c>
-      <c r="C283" s="5" t="e">
-        <v>#N/A</v>
+        <v>210</v>
+      </c>
+      <c r="C283" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
-        <v>335</v>
+        <v>113</v>
       </c>
       <c r="B284" t="s">
-        <v>295</v>
-      </c>
-      <c r="C284" s="5" t="e">
-        <v>#N/A</v>
+        <v>237</v>
+      </c>
+      <c r="C284" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
-        <v>188</v>
+        <v>217</v>
       </c>
       <c r="B285" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
-        <v>189</v>
+        <v>114</v>
       </c>
       <c r="B286" t="s">
-        <v>222</v>
+        <v>244</v>
       </c>
       <c r="C286" s="5" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B287" t="s">
-        <v>245</v>
-      </c>
-      <c r="C287" s="5">
-        <v>988</v>
+        <v>213</v>
+      </c>
+      <c r="C287" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B288" t="s">
-        <v>232</v>
-      </c>
-      <c r="C288" s="5" t="s">
-        <v>292</v>
+        <v>230</v>
+      </c>
+      <c r="C288" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B289" t="s">
-        <v>237</v>
-      </c>
-      <c r="C289" s="5" t="s">
-        <v>291</v>
+        <v>267</v>
+      </c>
+      <c r="C289" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
-        <v>113</v>
+        <v>274</v>
       </c>
       <c r="B290" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="C290" s="5">
         <v>988</v>
@@ -4689,266 +4786,123 @@
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B291" t="s">
-        <v>246</v>
-      </c>
-      <c r="C291" s="5">
-        <v>988</v>
+        <v>217</v>
+      </c>
+      <c r="C291" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
       <c r="B292" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="C292" s="5" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
-        <v>115</v>
+        <v>275</v>
       </c>
       <c r="B293" t="s">
-        <v>234</v>
+        <v>208</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
-        <v>209</v>
+        <v>120</v>
       </c>
       <c r="B294" t="s">
-        <v>219</v>
-      </c>
-      <c r="C294" s="5">
-        <v>988</v>
+        <v>208</v>
+      </c>
+      <c r="C294" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
-        <v>116</v>
+        <v>323</v>
       </c>
       <c r="B295" t="s">
-        <v>246</v>
-      </c>
-      <c r="C295" s="5">
-        <v>988</v>
+        <v>233</v>
+      </c>
+      <c r="C295" s="5" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
-        <v>226</v>
+        <v>183</v>
       </c>
       <c r="B296" t="s">
-        <v>218</v>
-      </c>
-      <c r="C296" s="5" t="e">
-        <v>#N/A</v>
+        <v>228</v>
+      </c>
+      <c r="C296" s="5" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B297" t="s">
-        <v>253</v>
-      </c>
-      <c r="C297" s="5" t="s">
-        <v>289</v>
+        <v>230</v>
+      </c>
+      <c r="C297" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
-        <v>118</v>
+        <v>276</v>
       </c>
       <c r="B298" t="s">
-        <v>222</v>
-      </c>
-      <c r="C298" s="5" t="s">
-        <v>289</v>
+        <v>230</v>
+      </c>
+      <c r="C298" s="5">
+        <v>988</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B299" t="s">
-        <v>239</v>
-      </c>
-      <c r="C299" s="5">
-        <v>988</v>
+        <v>222</v>
+      </c>
+      <c r="C299" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
-        <v>120</v>
+        <v>184</v>
       </c>
       <c r="B300" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="C300" s="5" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
-        <v>286</v>
+        <v>225</v>
       </c>
       <c r="B301" t="s">
-        <v>248</v>
-      </c>
-      <c r="C301" s="5">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A302" t="s">
-        <v>121</v>
-      </c>
-      <c r="B302" t="s">
-        <v>226</v>
-      </c>
-      <c r="C302" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A303" t="s">
-        <v>163</v>
-      </c>
-      <c r="B303" t="s">
-        <v>226</v>
-      </c>
-      <c r="C303" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A304" t="s">
-        <v>122</v>
-      </c>
-      <c r="B304" t="s">
-        <v>253</v>
-      </c>
-      <c r="C304" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A305" t="s">
-        <v>287</v>
-      </c>
-      <c r="B305" t="s">
-        <v>231</v>
-      </c>
-      <c r="C305" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A306" t="s">
-        <v>123</v>
-      </c>
-      <c r="B306" t="s">
-        <v>234</v>
-      </c>
-      <c r="C306" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A307" t="s">
-        <v>336</v>
-      </c>
-      <c r="B307" t="s">
-        <v>242</v>
-      </c>
-      <c r="C307" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A308" t="s">
-        <v>190</v>
-      </c>
-      <c r="B308" t="s">
-        <v>237</v>
-      </c>
-      <c r="C308" s="5" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A309" t="s">
-        <v>124</v>
-      </c>
-      <c r="B309" t="s">
-        <v>239</v>
-      </c>
-      <c r="C309" s="5">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A310" t="s">
-        <v>288</v>
-      </c>
-      <c r="B310" t="s">
-        <v>239</v>
-      </c>
-      <c r="C310" s="5">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A311" t="s">
-        <v>125</v>
-      </c>
-      <c r="B311" t="s">
-        <v>231</v>
-      </c>
-      <c r="C311" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A312" t="s">
-        <v>191</v>
-      </c>
-      <c r="B312" t="s">
-        <v>253</v>
-      </c>
-      <c r="C312" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A313" t="s">
-        <v>337</v>
-      </c>
-      <c r="B313" t="s">
-        <v>295</v>
-      </c>
-      <c r="C313" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A314" t="s">
-        <v>234</v>
-      </c>
-      <c r="B314" t="s">
-        <v>218</v>
-      </c>
-      <c r="C314" s="5" t="e">
-        <v>#N/A</v>
+        <v>209</v>
+      </c>
+      <c r="C301" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -4957,6 +4911,192 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B111710-BAF2-43B9-9BC3-BD186F8F2606}">
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="26.296875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.09765625" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.19921875" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.8984375" style="5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="B1" s="6">
+        <v>988</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B13" s="5" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B14" s="5" t="s">
+        <v>338</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C2BED81-0BFE-468A-AE72-18364B5A9D1C}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -4968,21 +5108,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="B1" t="s">
-        <v>304</v>
+        <v>291</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>306</v>
+        <v>293</v>
       </c>
       <c r="B2" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="C2" s="2">
         <v>988</v>
@@ -4990,46 +5130,46 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>310</v>
+        <v>297</v>
       </c>
       <c r="B3" t="s">
-        <v>307</v>
+        <v>294</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>311</v>
+        <v>298</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="B5" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>315</v>
+        <v>302</v>
       </c>
     </row>
   </sheetData>

--- a/attendance_raw.xlsx
+++ b/attendance_raw.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RegieSapico\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{818E2D59-9A0D-4D2F-831E-E604D02D731C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30F85CA8-41C2-4D5B-A819-290D3C4828D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31365" yWindow="1860" windowWidth="21015" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4890" yWindow="1665" windowWidth="21015" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="supervisor-program" sheetId="2" r:id="rId1"/>
@@ -1158,12 +1158,14 @@
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Verdana"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Verdana"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -4912,7 +4914,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B111710-BAF2-43B9-9BC3-BD186F8F2606}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.296875" style="5" bestFit="1" customWidth="1"/>
@@ -4958,7 +4960,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>327</v>
@@ -4975,7 +4977,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>328</v>
@@ -4989,7 +4991,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>329</v>
@@ -5003,7 +5005,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>330</v>
@@ -5017,7 +5019,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>331</v>
@@ -5028,7 +5030,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>332</v>
@@ -5039,7 +5041,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>333</v>
@@ -5050,7 +5052,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>334</v>
@@ -5061,7 +5063,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>335</v>
@@ -5071,9 +5073,6 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
-        <v>367</v>
-      </c>
       <c r="B12" s="5" t="s">
         <v>336</v>
       </c>
@@ -5089,6 +5088,11 @@
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B14" s="5" t="s">
         <v>338</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B15" s="5" t="s">
+        <v>358</v>
       </c>
     </row>
   </sheetData>

--- a/attendance_raw.xlsx
+++ b/attendance_raw.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RegieSapico\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30F85CA8-41C2-4D5B-A819-290D3C4828D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFED7595-5684-48B7-8AFB-661208563323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4890" yWindow="1665" windowWidth="21015" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="supervisor-program" sheetId="2" r:id="rId1"/>
@@ -4914,7 +4914,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B111710-BAF2-43B9-9BC3-BD186F8F2606}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.296875" style="5" bestFit="1" customWidth="1"/>
@@ -5084,15 +5084,13 @@
       <c r="B13" s="5" t="s">
         <v>337</v>
       </c>
+      <c r="C13" s="5" t="s">
+        <v>358</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B14" s="5" t="s">
         <v>338</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B15" s="5" t="s">
-        <v>358</v>
       </c>
     </row>
   </sheetData>

--- a/attendance_raw.xlsx
+++ b/attendance_raw.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RegieSapico\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFED7595-5684-48B7-8AFB-661208563323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62EFB66D-505B-41C6-B649-241135E3FD73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4890" yWindow="1665" windowWidth="21015" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="supervisor-program" sheetId="2" r:id="rId1"/>
@@ -5027,6 +5027,9 @@
       <c r="C7" s="5" t="s">
         <v>344</v>
       </c>
+      <c r="D7" s="5" t="s">
+        <v>358</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
@@ -5083,9 +5086,6 @@
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B13" s="5" t="s">
         <v>337</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">

--- a/attendance_raw.xlsx
+++ b/attendance_raw.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RegieSapico\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62EFB66D-505B-41C6-B649-241135E3FD73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C2E4C4E-36B6-4318-AC03-A2431EC86BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4890" yWindow="1665" windowWidth="21015" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4988,6 +4988,9 @@
       <c r="D4" s="5" t="s">
         <v>352</v>
       </c>
+      <c r="E4" s="5" t="s">
+        <v>358</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
@@ -5026,9 +5029,6 @@
       </c>
       <c r="C7" s="5" t="s">
         <v>344</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">

--- a/attendance_raw.xlsx
+++ b/attendance_raw.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RegieSapico\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C2E4C4E-36B6-4318-AC03-A2431EC86BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B11C2F3-393E-4E68-97A2-C3648B690A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4890" yWindow="1665" windowWidth="21015" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4988,9 +4988,6 @@
       <c r="D4" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>358</v>
-      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
@@ -5076,6 +5073,9 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>358</v>
+      </c>
       <c r="B12" s="5" t="s">
         <v>336</v>
       </c>

--- a/attendance_raw.xlsx
+++ b/attendance_raw.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RegieSapico\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B11C2F3-393E-4E68-97A2-C3648B690A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{972F3B10-BAE2-442C-ACA5-807B4188922A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4890" yWindow="1665" windowWidth="21015" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32595" yWindow="1785" windowWidth="21015" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="supervisor-program" sheetId="2" r:id="rId1"/>
@@ -4914,7 +4914,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B111710-BAF2-43B9-9BC3-BD186F8F2606}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.296875" style="5" bestFit="1" customWidth="1"/>
@@ -4943,7 +4943,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>326</v>
@@ -4960,7 +4960,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>327</v>
@@ -4977,7 +4977,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>328</v>
@@ -4991,7 +4991,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>329</v>
@@ -5005,7 +5005,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>330</v>
@@ -5019,7 +5019,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>331</v>
@@ -5030,7 +5030,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>332</v>
@@ -5041,7 +5041,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>333</v>
@@ -5052,7 +5052,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>334</v>
@@ -5063,7 +5063,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>335</v>
@@ -5073,9 +5073,6 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
-        <v>358</v>
-      </c>
       <c r="B12" s="5" t="s">
         <v>336</v>
       </c>
@@ -5091,6 +5088,11 @@
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B14" s="5" t="s">
         <v>338</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B15" s="5" t="s">
+        <v>357</v>
       </c>
     </row>
   </sheetData>
